--- a/99.Attachments/贵州亲子自驾行程-第三版.xlsx
+++ b/99.Attachments/贵州亲子自驾行程-第三版.xlsx
@@ -628,8 +628,8 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>全季酒店（观山湖）
-连住2晚</t>
+          <t>全季酒店（观山湖金融城店）
+连住3晚（D2-D4）</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -652,13 +652,15 @@
       <c r="C7" s="8" t="inlineStr">
         <is>
           <t>上午
-下午</t>
+下午
+傍晚</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
           <t>黔灵山公园（熊猫/猕猴/划船）
-贵阳欢乐世界或省地质博物馆</t>
+贵阳欢乐世界或省地质博物馆
+太平路夜市</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -912,7 +914,7 @@
         <is>
           <t>07:00
 11:30
-15:00</t>
+16:00</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">

--- a/99.Attachments/贵州亲子自驾行程-第三版.xlsx
+++ b/99.Attachments/贵州亲子自驾行程-第三版.xlsx
@@ -856,7 +856,8 @@
       <c r="E12" s="8" t="inlineStr">
         <is>
           <t>品兮.山前水下酒店
-连住2晚</t>
+（小七孔东门店）
+慢充过夜</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -879,18 +880,23 @@
       <c r="C13" s="8" t="inlineStr">
         <is>
           <t>08:00–15:00
+15:00
+下午
 傍晚</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>省力路线：卧龙潭→鸳鸯湖→翠谷瀑布→水上森林→小七孔古桥
-美食街</t>
+          <t>小七孔省力路线：卧龙潭→鸳鸯湖→翠谷瀑布→水上森林→小七孔古桥
+取车去荔波古镇（10min）
+入住曼居酒店（荔波店），古镇逛逛
+县城美食（酸汤鱼、杨梅汤）</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>续住品兮</t>
+          <t>曼居酒店（荔波店）
+慢充过夜</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">

--- a/99.Attachments/贵州亲子自驾行程-第三版.xlsx
+++ b/99.Attachments/贵州亲子自驾行程-第三版.xlsx
@@ -879,17 +879,15 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>08:00–15:00
-15:00
-下午
+          <t>08:00–17:00
+18:00
 傍晚</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
           <t>小七孔省力路线：卧龙潭→鸳鸯湖→翠谷瀑布→水上森林→小七孔古桥
-取车去荔波古镇（10min）
-入住曼居酒店（荔波店），古镇逛逛
+取车去荔波古镇，入住曼居酒店（荔波店）
 县城美食（酸汤鱼、杨梅汤）</t>
         </is>
       </c>
